--- a/docs/demo/client_campaign_tracker_v2.xlsx
+++ b/docs/demo/client_campaign_tracker_v2.xlsx
@@ -445,7 +445,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>act_366643171197739</t>
+          <t>act_000000000</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
